--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://czuvpraze-my.sharepoint.com/personal/xhroa008_studenti_czu_cz/Documents/Adam/ČZU/Bakalářská práce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1578" documentId="8_{80551DFE-DDF4-4F80-A9CF-49506F58725F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{82B8AD09-2BE7-4890-A8A3-EA2EC8A6E2EB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9773C62-EDB1-4E53-9911-B016FCAD50AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpoint" sheetId="1" r:id="rId1"/>
     <sheet name="entity" sheetId="6" r:id="rId2"/>
     <sheet name="DTO" sheetId="9" r:id="rId3"/>
     <sheet name="UI structure" sheetId="4" r:id="rId4"/>
-    <sheet name="etc" sheetId="8" r:id="rId5"/>
+    <sheet name="bus. postupy" sheetId="10" r:id="rId5"/>
+    <sheet name="etc" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="230">
   <si>
     <t>/login</t>
   </si>
@@ -115,12 +116,6 @@
     <t>Home</t>
   </si>
   <si>
-    <t>StudentOffers</t>
-  </si>
-  <si>
-    <t>StudentApplications</t>
-  </si>
-  <si>
     <t>Marketing, úvod, …</t>
   </si>
   <si>
@@ -142,31 +137,16 @@
     <t>3. úroveň</t>
   </si>
   <si>
-    <t>StudentOfferDetail</t>
-  </si>
-  <si>
     <t>Prohlížení současných nabídek</t>
   </si>
   <si>
-    <t>StudentApplicationDetail</t>
-  </si>
-  <si>
     <t>Detail, zrušení</t>
   </si>
   <si>
-    <t>EmployeeOffers</t>
-  </si>
-  <si>
     <t>Prohlížení skupinových nabídek</t>
   </si>
   <si>
     <t>Vytvoření nabídky</t>
-  </si>
-  <si>
-    <t>EmployeeOfferDetail</t>
-  </si>
-  <si>
-    <t>EmployeeOfferEdit</t>
   </si>
   <si>
     <t>Zrušení nabídky</t>
@@ -327,9 +307,6 @@
     <t>nabídka je v budoucnosti</t>
   </si>
   <si>
-    <t>OperatorApplications</t>
-  </si>
-  <si>
     <t>OperatorApplicationDetail</t>
   </si>
   <si>
@@ -342,9 +319,6 @@
     <t>OperatorGroupDetail</t>
   </si>
   <si>
-    <t>EmployeeOfferCreate</t>
-  </si>
-  <si>
     <t>OperatorGroupCreate</t>
   </si>
   <si>
@@ -382,12 +356,6 @@
   </si>
   <si>
     <t>vytvoření klienta</t>
-  </si>
-  <si>
-    <t>/operator/employee</t>
-  </si>
-  <si>
-    <t>přiřazen ke skupině</t>
   </si>
   <si>
     <t>DTO</t>
@@ -815,6 +783,148 @@
   </si>
   <si>
     <t>profilové info??</t>
+  </si>
+  <si>
+    <t>StudentJobOffers</t>
+  </si>
+  <si>
+    <t>StudentRegister</t>
+  </si>
+  <si>
+    <t>StudentJobOfferDetail</t>
+  </si>
+  <si>
+    <t>StudentJobApplications</t>
+  </si>
+  <si>
+    <t>StudentJobApplicationDetail</t>
+  </si>
+  <si>
+    <t>CustomerJobOffers</t>
+  </si>
+  <si>
+    <t>CustomerJobOfferCreate</t>
+  </si>
+  <si>
+    <t>CustomerJobOfferDetail</t>
+  </si>
+  <si>
+    <t>CustomerJobOfferEdit</t>
+  </si>
+  <si>
+    <t>OperatorJobApplications</t>
+  </si>
+  <si>
+    <t>/operator/customer</t>
+  </si>
+  <si>
+    <t>přiřazen ke skupině
+generovat heslo</t>
+  </si>
+  <si>
+    <t>registrace</t>
+  </si>
+  <si>
+    <t>ověření</t>
+  </si>
+  <si>
+    <t>přihlášení</t>
+  </si>
+  <si>
+    <t>prohlížení nabídek</t>
+  </si>
+  <si>
+    <t>přihlášení k nabídce</t>
+  </si>
+  <si>
+    <t>zrušení nabídky</t>
+  </si>
+  <si>
+    <t>příchod na práci</t>
+  </si>
+  <si>
+    <t>hodnocení (práce, op)</t>
+  </si>
+  <si>
+    <t>přijem odměny</t>
+  </si>
+  <si>
+    <t>prohlížení odměny</t>
+  </si>
+  <si>
+    <t>zrušení účtu</t>
+  </si>
+  <si>
+    <t>žádost o vytvoření skupiny</t>
+  </si>
+  <si>
+    <t>žádost o přidání účtu</t>
+  </si>
+  <si>
+    <t>vytvoření nabídky</t>
+  </si>
+  <si>
+    <t>úprava nabídky</t>
+  </si>
+  <si>
+    <t>prohlížení nabídek skupiny</t>
+  </si>
+  <si>
+    <t>práce</t>
+  </si>
+  <si>
+    <t>platba faktury</t>
+  </si>
+  <si>
+    <t>prohlížení faktury??? Balíčky??</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>ověření studenta</t>
+  </si>
+  <si>
+    <t>přijetí/zamítnutí přihlášky</t>
+  </si>
+  <si>
+    <t>kontrola nástupu na práci</t>
+  </si>
+  <si>
+    <t>hodnocení (studenta)</t>
+  </si>
+  <si>
+    <t>zrušení studentského účtu</t>
+  </si>
+  <si>
+    <t>obnovení studentského účtu</t>
+  </si>
+  <si>
+    <t>přidání účtu ke skupině</t>
+  </si>
+  <si>
+    <t>úprava skupiny</t>
+  </si>
+  <si>
+    <t>zrušení skupiny</t>
+  </si>
+  <si>
+    <t>úprava účtu (ověření?)</t>
+  </si>
+  <si>
+    <t>nastavení balíčku</t>
+  </si>
+  <si>
+    <t>úprava účtu (ověření)</t>
+  </si>
+  <si>
+    <t>promyslet koncept</t>
+  </si>
+  <si>
+    <t>možné úpravy</t>
+  </si>
+  <si>
+    <t>poznámky</t>
   </si>
 </sst>
 </file>
@@ -896,7 +1006,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -915,6 +1025,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -928,7 +1068,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -979,11 +1119,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="126">
+  <dxfs count="101">
     <dxf>
       <fill>
         <patternFill>
@@ -1015,6 +1171,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -1197,6 +1381,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1225,6 +1416,62 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -1351,6 +1598,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1379,6 +1633,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -1442,427 +1703,147 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2177,21 +2158,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE85A0F-B6B0-405B-B0DD-B998D5AB81FC}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="7"/>
-    <col min="2" max="2" width="8.85546875" style="3"/>
-    <col min="3" max="3" width="28.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="42.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="50.5703125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="28.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="50.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>8</v>
@@ -2203,21 +2184,21 @@
         <v>10</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>137</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
+        <v>228</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -2229,21 +2210,21 @@
         <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>137</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>227</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -2255,21 +2236,21 @@
         <v>12</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>138</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
+        <v>228</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -2278,7 +2259,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E4" s="7">
         <v>200</v>
@@ -2290,12 +2271,12 @@
         <v>14</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>139</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>229</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -2304,22 +2285,19 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2327,22 +2305,19 @@
         <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>139</v>
-      </c>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
@@ -2350,48 +2325,42 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E7" s="7">
         <v>200</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>139</v>
-      </c>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>139</v>
-      </c>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2399,418 +2368,320 @@
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>138</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>139</v>
-      </c>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E11" s="7">
         <v>200</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="G14" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>88</v>
+        <v>47</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>137</v>
-      </c>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>136</v>
-      </c>
+    <row r="25" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>136</v>
-      </c>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{9038D402-E177-457A-8E95-8EA79B9370D6}">
-            <xm:f>etc!$A$5</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="9" tint="0.59996337778862885"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{79B2C089-1606-42DF-8CB2-69DB6C24905F}">
-            <xm:f>etc!$A$4</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="7" tint="0.59996337778862885"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{1C489BDE-B729-4AE6-BF11-B7A8334E46A5}">
-            <xm:f>etc!$A$3</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="5" tint="0.39994506668294322"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{40C0CA4B-AE8E-4A70-9B84-427F32B74390}">
-            <xm:f>etc!$A$2</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.14996795556505021"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A1:A1048576</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB62C7DB-FCF9-44F8-87BB-63B51CAE9EDC}">
           <x14:formula1>
             <xm:f>etc!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A31</xm:sqref>
+          <xm:sqref>A16:A31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2821,14 +2692,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F046EC5E-0997-4F1F-89C0-BE0525D6DEB0}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.7109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="59.6640625" style="7" customWidth="1"/>
     <col min="2" max="2" width="47" style="7" customWidth="1"/>
     <col min="3" max="3" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>21</v>
       </c>
@@ -2839,70 +2710,70 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2914,17 +2785,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A883F13D-779A-4F28-80DB-FE086864C46C}">
   <dimension ref="A1:D121"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="49.88671875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>21</v>
@@ -2936,680 +2807,680 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C61" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C78" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C83" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C87" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C89" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C91" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C92" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C93" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C95" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C96" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C97" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C101" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C102" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C104" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C105" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C106" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C107" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C108" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C109" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C110" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C111" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C112" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C113" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C115" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C118" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C73" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C76" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C77" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B84" s="7" t="s">
+    </row>
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C89" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C91" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C92" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C93" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C95" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C96" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C97" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C98" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C99" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C101" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C102" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C104" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C105" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C106" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C107" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C108" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C109" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C110" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C111" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C112" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C113" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C115" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C116" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C118" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C119" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C120" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.25"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4677,156 +4548,156 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694BA3F6-B24A-4EB0-B375-4B8150629987}">
   <dimension ref="B1:E18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="62.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="E1" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>28</v>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="20" t="s">
+        <v>184</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>183</v>
       </c>
       <c r="E5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C10" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C11" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C14" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="D17" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
         <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4836,57 +4707,213 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="27.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>225</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8864AE-C8C6-47D9-9A9B-A8C6713BD64B}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9773C62-EDB1-4E53-9911-B016FCAD50AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED544AC-9B61-4974-91ED-B57F74F06D2E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpoint" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="DTO" sheetId="9" r:id="rId3"/>
     <sheet name="UI structure" sheetId="4" r:id="rId4"/>
     <sheet name="bus. postupy" sheetId="10" r:id="rId5"/>
-    <sheet name="etc" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="222">
   <si>
     <t>/login</t>
   </si>
@@ -94,13 +93,6 @@
     <t>nevytvářet student roli ale neověřenou roli</t>
   </si>
   <si>
-    <t>200 - ok</t>
-  </si>
-  <si>
-    <t>200 - ok
-404 - nenalezeno</t>
-  </si>
-  <si>
     <t>skrýt staré a již přihlášené</t>
   </si>
   <si>
@@ -116,15 +108,6 @@
     <t>Home</t>
   </si>
   <si>
-    <t>Marketing, úvod, …</t>
-  </si>
-  <si>
-    <t>Registrace</t>
-  </si>
-  <si>
-    <t>Přihlášení, zapomenuté heslo</t>
-  </si>
-  <si>
     <t>Funkce</t>
   </si>
   <si>
@@ -135,24 +118,6 @@
   </si>
   <si>
     <t>3. úroveň</t>
-  </si>
-  <si>
-    <t>Prohlížení současných nabídek</t>
-  </si>
-  <si>
-    <t>Detail, zrušení</t>
-  </si>
-  <si>
-    <t>Prohlížení skupinových nabídek</t>
-  </si>
-  <si>
-    <t>Vytvoření nabídky</t>
-  </si>
-  <si>
-    <t>Zrušení nabídky</t>
-  </si>
-  <si>
-    <t>Úprava nabídky</t>
   </si>
   <si>
     <t>Možné úpravy</t>
@@ -184,10 +149,6 @@
     <t>PUT</t>
   </si>
   <si>
-    <t>201 - vytvořeno
-400 - bus. log.</t>
-  </si>
-  <si>
     <t>vytvoření pracovní nabídky</t>
   </si>
   <si>
@@ -203,9 +164,6 @@
   </si>
   <si>
     <t>smazání pracovní nabídky</t>
-  </si>
-  <si>
-    <t>404 - nenalezeno</t>
   </si>
   <si>
     <t>smazání se zájemcem za strike</t>
@@ -310,9 +268,6 @@
     <t>OperatorApplicationDetail</t>
   </si>
   <si>
-    <t>Přijmutí/Zamítnutí nabídky</t>
-  </si>
-  <si>
     <t>OperatorGroups</t>
   </si>
   <si>
@@ -320,9 +275,6 @@
   </si>
   <si>
     <t>OperatorGroupCreate</t>
-  </si>
-  <si>
-    <t>Seznam skupin</t>
   </si>
   <si>
     <t>detail skupiny</t>
@@ -389,15 +341,491 @@
     <t>/operator/job-applications/:id</t>
   </si>
   <si>
-    <t>pouze nezpracované??</t>
-  </si>
-  <si>
     <t>potvrzení přihlášky
 zamítnutí přihlášky</t>
   </si>
   <si>
-    <t>204 - nic
-404 - nenalezeno</t>
+    <t>JobApplicationStateRequest
+JobApplicationResponse</t>
+  </si>
+  <si>
+    <t>JobApplicationDetailWithStudentResponse</t>
+  </si>
+  <si>
+    <t>response??</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>UserId
+Email
+PasswordHash
+PasswordSalt
+Role
+StudentId
+CustomerId</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>StudentId
+FirstName
+LastName
+DateOfBirth</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>CustomerId
+FirstName
+LastName
+GroupId</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>JobOffer</t>
+  </si>
+  <si>
+    <t>JobOfferId
+Title
+Description
+Wage
+Spaces
+Start
+End
+GroupId</t>
+  </si>
+  <si>
+    <t>JobApplication</t>
+  </si>
+  <si>
+    <t>JobApplicationId
+State
+StudentId
+JobOfferId</t>
+  </si>
+  <si>
+    <t>seznam skupin</t>
+  </si>
+  <si>
+    <t>/operator/groups</t>
+  </si>
+  <si>
+    <t>GroupResponse</t>
+  </si>
+  <si>
+    <t>GroupResponse
+GroupRequest</t>
+  </si>
+  <si>
+    <t>/operator/groups/:id</t>
+  </si>
+  <si>
+    <t>GroupWithCustomersResponse</t>
+  </si>
+  <si>
+    <t>OperatorCustomerCreate</t>
+  </si>
+  <si>
+    <t>vytvoření zákazníka</t>
+  </si>
+  <si>
+    <t>není v minulosti</t>
+  </si>
+  <si>
+    <t>seznam pracovních nabídek</t>
+  </si>
+  <si>
+    <t>detail pracovní nabídky</t>
+  </si>
+  <si>
+    <t>zrušení přihlášky</t>
+  </si>
+  <si>
+    <t>Stav</t>
+  </si>
+  <si>
+    <t>návrh</t>
+  </si>
+  <si>
+    <t>vývoj</t>
+  </si>
+  <si>
+    <t>hotovo</t>
+  </si>
+  <si>
+    <t>detaily</t>
+  </si>
+  <si>
+    <t>konkurence</t>
+  </si>
+  <si>
+    <t>musí být v budoucnosti
+není potvrzený zájemce
+pouze měnit status??</t>
+  </si>
+  <si>
+    <t>AuthenticateResponse</t>
+  </si>
+  <si>
+    <t>AuthenticateRequest</t>
+  </si>
+  <si>
+    <t>StudentRequest</t>
+  </si>
+  <si>
+    <t>délka, znaky</t>
+  </si>
+  <si>
+    <t>validní mail</t>
+  </si>
+  <si>
+    <t>StudentResponse</t>
+  </si>
+  <si>
+    <t>JobApplicationRequest</t>
+  </si>
+  <si>
+    <t>JobApplicationResponse</t>
+  </si>
+  <si>
+    <t>JobOfferRequest</t>
+  </si>
+  <si>
+    <t>JobOfferResponse</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>GroupRequest</t>
+  </si>
+  <si>
+    <t>GroupId
+Name</t>
+  </si>
+  <si>
+    <t>GroupId</t>
+  </si>
+  <si>
+    <t>CustomerResponse</t>
+  </si>
+  <si>
+    <t>CustomerRequest</t>
+  </si>
+  <si>
+    <t>JobApplicationStateRequest</t>
+  </si>
+  <si>
+    <t>StudentRequest
+StudentResponse</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Token</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>JobOfferId</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Wage</t>
+  </si>
+  <si>
+    <t>Spaces</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>validace</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>FreeSpaces</t>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>JobApplicationId</t>
+  </si>
+  <si>
+    <t>JobOfferDetailWithStudentsResponse</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Students </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(StudentSimpleResponse)</t>
+    </r>
+  </si>
+  <si>
+    <t>StudentSimpleResponse</t>
+  </si>
+  <si>
+    <t>StudentId</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Customers </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CustomerSimpleResponse)</t>
+    </r>
+  </si>
+  <si>
+    <t>CustomerId</t>
+  </si>
+  <si>
+    <t>CustomerSimleResponse</t>
+  </si>
+  <si>
+    <t>datum podání</t>
+  </si>
+  <si>
+    <t>StudentJobOffers</t>
+  </si>
+  <si>
+    <t>StudentRegister</t>
+  </si>
+  <si>
+    <t>StudentJobOfferDetail</t>
+  </si>
+  <si>
+    <t>StudentJobApplications</t>
+  </si>
+  <si>
+    <t>StudentJobApplicationDetail</t>
+  </si>
+  <si>
+    <t>CustomerJobOffers</t>
+  </si>
+  <si>
+    <t>CustomerJobOfferCreate</t>
+  </si>
+  <si>
+    <t>CustomerJobOfferDetail</t>
+  </si>
+  <si>
+    <t>CustomerJobOfferEdit</t>
+  </si>
+  <si>
+    <t>OperatorJobApplications</t>
+  </si>
+  <si>
+    <t>/operator/customer</t>
+  </si>
+  <si>
+    <t>registrace</t>
+  </si>
+  <si>
+    <t>ověření</t>
+  </si>
+  <si>
+    <t>přihlášení</t>
+  </si>
+  <si>
+    <t>prohlížení nabídek</t>
+  </si>
+  <si>
+    <t>přihlášení k nabídce</t>
+  </si>
+  <si>
+    <t>zrušení nabídky</t>
+  </si>
+  <si>
+    <t>příchod na práci</t>
+  </si>
+  <si>
+    <t>hodnocení (práce, op)</t>
+  </si>
+  <si>
+    <t>přijem odměny</t>
+  </si>
+  <si>
+    <t>prohlížení odměny</t>
+  </si>
+  <si>
+    <t>zrušení účtu</t>
+  </si>
+  <si>
+    <t>žádost o vytvoření skupiny</t>
+  </si>
+  <si>
+    <t>žádost o přidání účtu</t>
+  </si>
+  <si>
+    <t>vytvoření nabídky</t>
+  </si>
+  <si>
+    <t>úprava nabídky</t>
+  </si>
+  <si>
+    <t>prohlížení nabídek skupiny</t>
+  </si>
+  <si>
+    <t>práce</t>
+  </si>
+  <si>
+    <t>platba faktury</t>
+  </si>
+  <si>
+    <t>prohlížení faktury??? Balíčky??</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>ověření studenta</t>
+  </si>
+  <si>
+    <t>přijetí/zamítnutí přihlášky</t>
+  </si>
+  <si>
+    <t>kontrola nástupu na práci</t>
+  </si>
+  <si>
+    <t>hodnocení (studenta)</t>
+  </si>
+  <si>
+    <t>zrušení studentského účtu</t>
+  </si>
+  <si>
+    <t>obnovení studentského účtu</t>
+  </si>
+  <si>
+    <t>přidání účtu ke skupině</t>
+  </si>
+  <si>
+    <t>úprava skupiny</t>
+  </si>
+  <si>
+    <t>zrušení skupiny</t>
+  </si>
+  <si>
+    <t>úprava účtu (ověření?)</t>
+  </si>
+  <si>
+    <t>nastavení balíčku</t>
+  </si>
+  <si>
+    <t>úprava účtu (ověření)</t>
+  </si>
+  <si>
+    <t>promyslet koncept</t>
+  </si>
+  <si>
+    <t>možné úpravy</t>
+  </si>
+  <si>
+    <t>poznámky</t>
+  </si>
+  <si>
+    <t>marketing, úvod, …</t>
+  </si>
+  <si>
+    <t>přihlášení, zapomenuté heslo</t>
+  </si>
+  <si>
+    <t>prohlížení současných nabídek</t>
+  </si>
+  <si>
+    <t>detail, zrušení</t>
+  </si>
+  <si>
+    <t>prohlížení skupinových nabídek</t>
+  </si>
+  <si>
+    <t>přijmutí/zamítnutí nabídky</t>
+  </si>
+  <si>
+    <t>vrátit i uživatelé</t>
+  </si>
+  <si>
+    <t>unikátní jméno</t>
+  </si>
+  <si>
+    <t>vybrat bus. plan?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>přiřazen ke skupině</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+generovat heslo</t>
+    </r>
+  </si>
+  <si>
+    <t>pouze nezpracované</t>
   </si>
   <si>
     <r>
@@ -416,29 +844,6 @@
       </rPr>
       <t>je nezpracovaná</t>
     </r>
-  </si>
-  <si>
-    <t>JobApplicationStateRequest
-JobApplicationResponse</t>
-  </si>
-  <si>
-    <t>JobApplicationDetailWithStudentResponse</t>
-  </si>
-  <si>
-    <t>response??</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pouze nezpracované</t>
-    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -449,482 +854,67 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-pouze nové ??</t>
-    </r>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>UserId
-Email
-PasswordHash
-PasswordSalt
-Role
-StudentId
-CustomerId</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
-    <t>StudentId
-FirstName
-LastName
-DateOfBirth</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>CustomerId
-FirstName
-LastName
-GroupId</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>JobOffer</t>
-  </si>
-  <si>
-    <t>JobOfferId
-Title
-Description
-Wage
-Spaces
-Start
-End
-GroupId</t>
-  </si>
-  <si>
-    <t>JobApplication</t>
-  </si>
-  <si>
-    <t>JobApplicationId
-State
-StudentId
-JobOfferId</t>
-  </si>
-  <si>
-    <t>seznam skupin</t>
-  </si>
-  <si>
-    <t>/operator/groups</t>
-  </si>
-  <si>
-    <t>GroupResponse</t>
-  </si>
-  <si>
-    <t>GroupResponse
-GroupRequest</t>
-  </si>
-  <si>
-    <t>/operator/groups/:id</t>
-  </si>
-  <si>
-    <t>i uživatelé</t>
-  </si>
-  <si>
-    <t>GroupWithCustomersResponse</t>
-  </si>
-  <si>
-    <t>OperatorCustomerCreate</t>
-  </si>
-  <si>
-    <t>vytvoření zákazníka</t>
-  </si>
-  <si>
-    <t>není v minulosti</t>
-  </si>
-  <si>
-    <t>200
-404
-400</t>
-  </si>
-  <si>
-    <t>201
-400</t>
-  </si>
-  <si>
-    <t>204
-400
-404</t>
-  </si>
-  <si>
-    <t>seznam pracovních nabídek</t>
-  </si>
-  <si>
-    <t>detail pracovní nabídky</t>
-  </si>
-  <si>
-    <t>zrušení přihlášky</t>
-  </si>
-  <si>
-    <t>HTTP status</t>
-  </si>
-  <si>
-    <t>200
-400
-404</t>
-  </si>
-  <si>
-    <t>Stav</t>
-  </si>
-  <si>
-    <t>návrh</t>
-  </si>
-  <si>
-    <t>vývoj</t>
-  </si>
-  <si>
-    <t>hotovo</t>
-  </si>
-  <si>
-    <t>detaily</t>
-  </si>
-  <si>
-    <t>konkurence</t>
-  </si>
-  <si>
-    <t>musí být v budoucnosti
-není potvrzený zájemce
-pouze měnit status??</t>
-  </si>
-  <si>
-    <t>AuthenticateResponse</t>
-  </si>
-  <si>
-    <t>AuthenticateRequest</t>
-  </si>
-  <si>
-    <t>StudentRequest</t>
-  </si>
-  <si>
-    <t>délka, znaky</t>
-  </si>
-  <si>
-    <t>validní mail</t>
-  </si>
-  <si>
-    <t>StudentResponse</t>
-  </si>
-  <si>
-    <t>JobApplicationRequest</t>
-  </si>
-  <si>
-    <t>JobApplicationResponse</t>
-  </si>
-  <si>
-    <t>JobOfferRequest</t>
-  </si>
-  <si>
-    <t>JobOfferResponse</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>GroupRequest</t>
-  </si>
-  <si>
-    <t>GroupId
-Name</t>
-  </si>
-  <si>
-    <t>GroupId</t>
-  </si>
-  <si>
-    <t>CustomerResponse</t>
-  </si>
-  <si>
-    <t>CustomerRequest</t>
-  </si>
-  <si>
-    <t>JobApplicationStateRequest</t>
-  </si>
-  <si>
-    <t>StudentRequest
-StudentResponse</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Token</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>DateOfBirth</t>
-  </si>
-  <si>
-    <t>JobOfferId</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Wage</t>
-  </si>
-  <si>
-    <t>Spaces</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>End</t>
-  </si>
-  <si>
-    <t>stavEndpt</t>
-  </si>
-  <si>
-    <t>stavDTO</t>
-  </si>
-  <si>
-    <t>validace</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>FreeSpaces</t>
-  </si>
-  <si>
-    <t>GroupName</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>JobApplicationId</t>
-  </si>
-  <si>
-    <t>JobOfferDetailWithStudentsResponse</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Students </t>
+</t>
     </r>
     <r>
       <rPr>
-        <i/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(StudentSimpleResponse)</t>
+      <t>měnit pouze stav</t>
     </r>
   </si>
   <si>
-    <t>StudentSimpleResponse</t>
-  </si>
-  <si>
-    <t>StudentId</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Customers </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(CustomerSimpleResponse)</t>
-    </r>
-  </si>
-  <si>
-    <t>CustomerId</t>
-  </si>
-  <si>
-    <t>CustomerSimleResponse</t>
+    <t>další info</t>
+  </si>
+  <si>
+    <t>datum registrace</t>
+  </si>
+  <si>
+    <t>poznámky
+promyslet hodnocení
+promyslet aktivaci</t>
   </si>
   <si>
     <t>adresa
-kontakty
-sro, …
-hodnocení</t>
-  </si>
-  <si>
-    <t>datum podání</t>
+další info</t>
+  </si>
+  <si>
+    <t>poznámky
+promyslet hodnocení
+promyslet bus plan</t>
   </si>
   <si>
     <t>adresa
+další info
 datum vytvoření</t>
   </si>
   <si>
-    <t>profilové info</t>
-  </si>
-  <si>
     <t>adresa
-hodnocení
-profilové info</t>
-  </si>
-  <si>
-    <t>profilové info??</t>
-  </si>
-  <si>
-    <t>StudentJobOffers</t>
-  </si>
-  <si>
-    <t>StudentRegister</t>
-  </si>
-  <si>
-    <t>StudentJobOfferDetail</t>
-  </si>
-  <si>
-    <t>StudentJobApplications</t>
-  </si>
-  <si>
-    <t>StudentJobApplicationDetail</t>
-  </si>
-  <si>
-    <t>CustomerJobOffers</t>
-  </si>
-  <si>
-    <t>CustomerJobOfferCreate</t>
-  </si>
-  <si>
-    <t>CustomerJobOfferDetail</t>
-  </si>
-  <si>
-    <t>CustomerJobOfferEdit</t>
-  </si>
-  <si>
-    <t>OperatorJobApplications</t>
-  </si>
-  <si>
-    <t>/operator/customer</t>
-  </si>
-  <si>
-    <t>přiřazen ke skupině
-generovat heslo</t>
-  </si>
-  <si>
-    <t>registrace</t>
-  </si>
-  <si>
-    <t>ověření</t>
-  </si>
-  <si>
-    <t>přihlášení</t>
-  </si>
-  <si>
-    <t>prohlížení nabídek</t>
-  </si>
-  <si>
-    <t>přihlášení k nabídce</t>
-  </si>
-  <si>
-    <t>zrušení nabídky</t>
-  </si>
-  <si>
-    <t>příchod na práci</t>
-  </si>
-  <si>
-    <t>hodnocení (práce, op)</t>
-  </si>
-  <si>
-    <t>přijem odměny</t>
-  </si>
-  <si>
-    <t>prohlížení odměny</t>
-  </si>
-  <si>
-    <t>zrušení účtu</t>
-  </si>
-  <si>
-    <t>žádost o vytvoření skupiny</t>
-  </si>
-  <si>
-    <t>žádost o přidání účtu</t>
-  </si>
-  <si>
-    <t>vytvoření nabídky</t>
-  </si>
-  <si>
-    <t>úprava nabídky</t>
-  </si>
-  <si>
-    <t>prohlížení nabídek skupiny</t>
-  </si>
-  <si>
-    <t>práce</t>
-  </si>
-  <si>
-    <t>platba faktury</t>
-  </si>
-  <si>
-    <t>prohlížení faktury??? Balíčky??</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>ověření studenta</t>
-  </si>
-  <si>
-    <t>přijetí/zamítnutí přihlášky</t>
-  </si>
-  <si>
-    <t>kontrola nástupu na práci</t>
-  </si>
-  <si>
-    <t>hodnocení (studenta)</t>
-  </si>
-  <si>
-    <t>zrušení studentského účtu</t>
-  </si>
-  <si>
-    <t>obnovení studentského účtu</t>
-  </si>
-  <si>
-    <t>přidání účtu ke skupině</t>
-  </si>
-  <si>
-    <t>úprava skupiny</t>
-  </si>
-  <si>
-    <t>zrušení skupiny</t>
-  </si>
-  <si>
-    <t>úprava účtu (ověření?)</t>
-  </si>
-  <si>
-    <t>nastavení balíčku</t>
-  </si>
-  <si>
-    <t>úprava účtu (ověření)</t>
-  </si>
-  <si>
-    <t>promyslet koncept</t>
-  </si>
-  <si>
-    <t>možné úpravy</t>
-  </si>
-  <si>
-    <t>poznámky</t>
+datum vytvoření
+kategorie?</t>
+  </si>
+  <si>
+    <t>Adresa?</t>
+  </si>
+  <si>
+    <t>Smlouva?</t>
+  </si>
+  <si>
+    <t>Baliček?</t>
+  </si>
+  <si>
+    <t>Hodnoceni?</t>
+  </si>
+  <si>
+    <t>PracovniPotvrzeni?</t>
+  </si>
+  <si>
+    <t>Vyplatnice?</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +996,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1051,7 +1041,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1068,7 +1070,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1125,7 +1127,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1135,39 +1136,24 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="101">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="97">
     <dxf>
       <fill>
         <patternFill>
@@ -2157,22 +2143,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE85A0F-B6B0-405B-B0DD-B998D5AB81FC}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="3" width="28.109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="42.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="50.5546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="3"/>
+    <col min="3" max="3" width="28.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="50.5703125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>8</v>
@@ -2183,22 +2168,19 @@
       <c r="D1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>122</v>
+      <c r="E1" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>228</v>
+        <v>27</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>195</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -2209,22 +2191,19 @@
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>227</v>
+      <c r="G2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>194</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -2235,22 +2214,19 @@
       <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>40</v>
+      <c r="E3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
-        <v>228</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>195</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -2259,24 +2235,21 @@
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="7">
-        <v>200</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
-        <v>229</v>
+      <c r="G4" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -2285,19 +2258,19 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>196</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2305,19 +2278,19 @@
         <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>195</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,42 +2298,39 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="7">
-        <v>200</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G7" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>195</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2368,307 +2338,322 @@
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="7">
-        <v>200</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>196</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>100</v>
+      </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>100</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>194</v>
+      </c>
       <c r="B17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>196</v>
+      </c>
       <c r="B18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>102</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>196</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>194</v>
+      </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>194</v>
+      </c>
       <c r="B23" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>194</v>
+      </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>194</v>
+      </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>194</v>
+      </c>
       <c r="B26" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2679,9 +2664,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB62C7DB-FCF9-44F8-87BB-63B51CAE9EDC}">
           <x14:formula1>
-            <xm:f>etc!$A$2:$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>A16:A31</xm:sqref>
+          <xm:sqref>A27:A31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2691,89 +2676,159 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F046EC5E-0997-4F1F-89C0-BE0525D6DEB0}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="47" style="7" customWidth="1"/>
-    <col min="3" max="3" width="68" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="47" style="7" customWidth="1"/>
+    <col min="4" max="4" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C1" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="18" t="s">
+    <row r="2" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>178</v>
+      <c r="B8" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2785,702 +2840,702 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A883F13D-779A-4F28-80DB-FE086864C46C}">
   <dimension ref="A1:D121"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="49.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="6" t="s">
+    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C80" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C83" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C89" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C101" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B117" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    </row>
+    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C119" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C83" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C85" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C87" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C88" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C89" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C91" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C92" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C95" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C96" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C101" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C102" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C104" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C105" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C107" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C115" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C118" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C119" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C120" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3489,7 +3544,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="82" operator="equal" id="{F7887BE8-9DAF-443D-8379-9B1344CB8E98}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3499,7 +3554,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="119" operator="equal" id="{0DA4A752-8956-418D-B9B2-20CEF47590C2}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3509,7 +3564,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="120" operator="equal" id="{2B9B1C6D-E708-4EF4-B222-51F429F4BAD7}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3519,7 +3574,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="121" operator="equal" id="{C9E0AE8C-4750-457E-943D-BEECC688297F}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3529,7 +3584,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="122" operator="equal" id="{1363F115-7AEC-4135-B44A-4CA8A5DE918B}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3542,7 +3597,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="83" operator="equal" id="{211280A5-7598-4C9D-AAF9-DD37B111D6DC}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3552,7 +3607,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="84" operator="equal" id="{08C3EEE2-3D2D-4989-9014-590EB4BAFD1D}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3562,7 +3617,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="85" operator="equal" id="{D0F20C67-C9E4-47F3-9883-B6C5E09AB135}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3572,7 +3627,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="86" operator="equal" id="{19BC2AB0-5EF5-4270-820B-9419C7869672}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3585,7 +3640,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="103" operator="equal" id="{2BE2A008-5CB0-4750-B44A-824E776776D7}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3595,7 +3650,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="104" operator="equal" id="{D418F342-3192-4C05-9791-E668571088A0}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3605,7 +3660,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="105" operator="equal" id="{D31A8ABC-E52F-400B-AFD5-55CB480A11A2}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3615,7 +3670,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="106" operator="equal" id="{AAE3A609-2DC8-45A5-A826-8F673A82D51D}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3628,7 +3683,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="99" operator="equal" id="{9362BF1C-6B99-4F29-B0C5-2D29C0E4E7F7}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3638,7 +3693,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="100" operator="equal" id="{AC3D962B-04BB-46FD-9F9D-61BE24FEFF46}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3648,7 +3703,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="101" operator="equal" id="{DE073717-E618-4A6D-BE35-505F9B6548DC}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3658,7 +3713,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="102" operator="equal" id="{B2CB44C4-5A1A-4514-9734-27B4B4785D78}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3671,7 +3726,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="91" operator="equal" id="{666D9B8A-5A98-46FA-AF46-98623E6DA86B}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3681,7 +3736,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="92" operator="equal" id="{B1C5D1A8-92CA-42DA-BF68-973DF14AE369}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3691,7 +3746,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="93" operator="equal" id="{F9C83D8E-5F91-4A70-92C3-CF121A6137DE}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3701,7 +3756,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="94" operator="equal" id="{7CED8FD9-6DE5-4085-BEDB-0762FA1E9712}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3714,7 +3769,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="87" operator="equal" id="{7F397E4C-8E96-4D7A-AB08-FF2F1DD1A3C1}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3724,7 +3779,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="88" operator="equal" id="{18F2FB5B-6DE6-44FD-BF84-B6351C83AB51}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3734,7 +3789,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="89" operator="equal" id="{23CB5C05-4131-4225-89D6-1D0E01773F8B}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3744,7 +3799,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="90" operator="equal" id="{0AF5EF6C-03E2-4F42-9BC9-1A8D39447AE8}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3757,7 +3812,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="77" operator="equal" id="{FC6EAC8F-E702-4DCA-B18B-C369AC5F7764}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3767,7 +3822,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="78" operator="equal" id="{4B22912F-7A48-4A4E-B78C-1FCE47836E14}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3777,7 +3832,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="79" operator="equal" id="{73121C3B-9F23-4068-BE30-342443DBFB13}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3787,7 +3842,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="80" operator="equal" id="{51ED1F5A-BB66-45C2-8615-8E50A1DB7172}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3797,7 +3852,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="81" operator="equal" id="{46F995C5-7929-4E48-A230-CDBD04FB6B01}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3810,7 +3865,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="67" operator="equal" id="{1CCB4E0D-04EB-403E-B52F-A35BB268A7B0}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3820,7 +3875,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="68" operator="equal" id="{17DDF9AA-7FD1-4700-A73F-67838C0C11FE}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3830,7 +3885,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="69" operator="equal" id="{54E92BC6-1538-4A11-AC21-89E6C5C45695}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3840,7 +3895,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="70" operator="equal" id="{4A06DA58-8167-47E1-A6FF-691017D6A47A}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3850,7 +3905,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="71" operator="equal" id="{5F5A5633-76C3-411F-82EB-939EB5171B7B}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3863,7 +3918,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="62" operator="equal" id="{A568D34F-9146-444F-97FD-4CE11FFE2F86}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3873,7 +3928,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="63" operator="equal" id="{49CB4E50-A438-4AA1-A4B5-D78705A75BC3}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3883,7 +3938,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="64" operator="equal" id="{511FE4CC-9145-492A-8FA1-66FDF26DEFB7}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3893,7 +3948,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="65" operator="equal" id="{FBDA7234-7ECF-49DE-9E8D-6C552F367A12}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3903,7 +3958,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="66" operator="equal" id="{87E018F9-8EDC-4C19-8C66-73A20259AF6E}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3916,7 +3971,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="57" operator="equal" id="{D23E356C-E955-4337-91FA-CA518A0522A5}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3926,7 +3981,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="58" operator="equal" id="{B6BD99EF-9893-424B-9A23-013A9C21B7D9}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3936,7 +3991,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="59" operator="equal" id="{57A22D01-7323-4A38-A8CA-E82C2A42F297}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3946,7 +4001,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="60" operator="equal" id="{C6FF99AD-5954-4DBE-B871-F908F74A2E0E}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3956,7 +4011,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="61" operator="equal" id="{7E1AC14E-B4ED-412F-8A62-53CBE42EF8F0}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3969,7 +4024,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="53" operator="equal" id="{6D262399-0E9B-4723-95AF-7C63EAE9F1DD}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3979,7 +4034,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="54" operator="equal" id="{9D3F6F3D-5867-43C7-8056-F154A74C3E99}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3989,7 +4044,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="55" operator="equal" id="{841E436F-F4D4-4F8A-97C3-D923815044BD}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3999,7 +4054,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="56" operator="equal" id="{6521DF8B-0365-426D-BB90-A346C6CBA7BC}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4012,7 +4067,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="49" operator="equal" id="{A32412AB-56A9-4EB4-9227-898AC37EE230}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4022,7 +4077,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="50" operator="equal" id="{9BCFC188-5375-4C26-93B6-7614CC6B9ACE}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4032,7 +4087,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="51" operator="equal" id="{EA69D32A-D26B-4EAF-9C46-2A0EA59282D0}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4042,7 +4097,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="52" operator="equal" id="{69C5411F-4CCD-4EB4-8F64-BDEAF873DB92}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4055,7 +4110,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="44" operator="equal" id="{36160C97-3AF9-4A62-AD5B-EECB0BCF0724}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4065,7 +4120,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="45" operator="equal" id="{1F7D6EA9-5FC0-4D00-A8C7-4501DFD3B2E3}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4075,7 +4130,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="46" operator="equal" id="{45FB2805-3432-494F-93CA-22CA3A436C01}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4085,7 +4140,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="47" operator="equal" id="{502E3F8D-598C-49B5-A405-4C4E712FF30A}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4095,7 +4150,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="48" operator="equal" id="{10F4B565-D174-4C6F-B6D1-5619466FF8EB}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4108,7 +4163,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="40" operator="equal" id="{AEF8A41B-34D5-4E27-AD7D-04E4740D4ED6}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4118,7 +4173,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="41" operator="equal" id="{681C74CE-6405-4942-A059-23AF3C3F8C2B}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4128,7 +4183,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="42" operator="equal" id="{9A19FF32-C3BA-4D3C-BE86-EFB27A593649}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4138,7 +4193,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="43" operator="equal" id="{F2CC705D-1EC1-4E87-88E3-F81ADFAF6D74}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4151,7 +4206,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="36" operator="equal" id="{9FBEF4DE-9830-4E78-94B1-C4B9D00468FB}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4161,7 +4216,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="37" operator="equal" id="{F885C240-DCD8-41FE-9515-2344B175793C}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4171,7 +4226,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="38" operator="equal" id="{463652C7-A9D5-4455-8048-FA866CF16D45}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4181,7 +4236,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="39" operator="equal" id="{5256EECB-E489-4961-A8D2-6573EDE0C478}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4194,7 +4249,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="31" operator="equal" id="{97244BFD-DCBD-4D77-8205-13EFC034893F}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4204,7 +4259,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="32" operator="equal" id="{3D255B44-A0C7-4B44-80D5-449DF104BC70}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4214,7 +4269,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="33" operator="equal" id="{E0D4E59F-5B06-4D31-80A8-B1546BEC2C84}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4224,7 +4279,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="34" operator="equal" id="{A08ADAAA-615B-4126-AB04-2B5824060906}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4234,7 +4289,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="35" operator="equal" id="{6E4A284A-C7AB-4CE1-8589-B1C9D1BE3F4C}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4247,7 +4302,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="27" operator="equal" id="{F00A58E5-9A45-4BF8-9CC1-B55B0345462C}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4257,7 +4312,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="28" operator="equal" id="{7A59C23C-5A4A-4F2C-96B9-4D2725C09642}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4267,7 +4322,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="29" operator="equal" id="{1CD902B0-87F3-4CD6-83E3-69E42C4C0248}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4277,7 +4332,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="30" operator="equal" id="{C28F55D4-D406-416A-841E-C854790EDC88}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4290,7 +4345,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="23" operator="equal" id="{C00A5103-C748-4496-8694-03E4EEA34CAE}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4300,7 +4355,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="24" operator="equal" id="{48AA1A1A-4C8B-4B39-B2B8-E3D476C852BF}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4310,7 +4365,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="25" operator="equal" id="{82CC45F8-10E4-431D-B319-7A5B52017D00}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4320,7 +4375,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="26" operator="equal" id="{8997F925-BCC4-489A-9E0A-536043DC5079}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4333,7 +4388,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="19" operator="equal" id="{C4F32E96-1B55-4F35-826B-EA419733095D}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4343,7 +4398,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="20" operator="equal" id="{4C9318D4-ED42-49EB-8BE1-C3C690106323}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4353,7 +4408,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="21" operator="equal" id="{70F1ED74-EF6D-4256-88EC-498932667E3C}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4363,7 +4418,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="22" operator="equal" id="{A30F8A19-D0A5-4F63-80BF-CDA7CEBB238B}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4376,7 +4431,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="10" operator="equal" id="{F4926574-1470-4438-8C5A-A690375BBB96}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4386,7 +4441,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="11" operator="equal" id="{2AD9965E-6A4F-4DC2-A061-A14001489DE4}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4396,7 +4451,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="12" operator="equal" id="{AEDFE6AA-E713-49D3-98E5-A86D87F0E3B2}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4406,7 +4461,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="13" operator="equal" id="{A8B9EB16-109F-4F08-A4FE-F546FE5450A1}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4416,7 +4471,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="14" operator="equal" id="{B7EF4893-EDBD-455C-9A63-B7E303337FC4}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4429,7 +4484,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="6" operator="equal" id="{86138CAC-C363-4DA5-BCB8-7E42CFFDCCA4}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4439,7 +4494,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="7" operator="equal" id="{1DF60DE6-8123-4AC9-9C93-DB9E64D4B47C}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4449,7 +4504,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="8" operator="equal" id="{CCB97F3B-F745-4AAA-A682-7A357C66F9B2}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4459,7 +4514,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="9" operator="equal" id="{CCFF2097-E4F4-40C8-9311-5AE3624ED734}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4472,7 +4527,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="1" operator="equal" id="{791EAEA4-1F88-4AFA-A9A5-B87696D305D5}">
-            <xm:f>etc!$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4482,7 +4537,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="2" operator="equal" id="{FA28BFDC-663C-4EEF-8572-591943711AEC}">
-            <xm:f>etc!$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4492,7 +4547,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="3" operator="equal" id="{A19656C1-9B10-4940-8908-4D83DBC59FC5}">
-            <xm:f>etc!$A$4</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4502,7 +4557,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="4" operator="equal" id="{C094CC99-72B5-4D69-97EE-BC3CD2ABCE78}">
-            <xm:f>etc!$A$3</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4512,7 +4567,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="5" operator="equal" id="{2726082C-B0DF-4620-B1BA-3448F20820E8}">
-            <xm:f>etc!$A$2</xm:f>
+            <xm:f>#REF!</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4529,13 +4584,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8910B38B-79B6-4CCB-A1B0-31F905D2CB03}">
           <x14:formula1>
-            <xm:f>etc!$A$2:$A$5</xm:f>
+            <xm:f>#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>A47 A41 A39 A27 A20 A58 A68 A79 A82 A90 A117 A86 A100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{82F4869F-9F7D-4ACA-B92F-8B8E78BCA95F}">
           <x14:formula1>
-            <xm:f>etc!$B$2:$B$6</xm:f>
+            <xm:f>#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>A2 A5 A37 A15 A9 A72 A84 A94 A114</xm:sqref>
         </x14:dataValidation>
@@ -4548,156 +4603,156 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694BA3F6-B24A-4EB0-B375-4B8150629987}">
   <dimension ref="B1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="62.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C4" s="20" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C6" s="20" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C8" s="20" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C10" s="20" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C11" s="20" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C14" s="20" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C16" s="20" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="D17" s="21" t="s">
-        <v>113</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>65</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4709,151 +4764,151 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="5" max="5" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>206</v>
+        <v>162</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>173</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>207</v>
+        <v>163</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>174</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>201</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>168</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>211</v>
+        <v>169</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>178</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
-        <v>203</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>170</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>212</v>
+        <v>171</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>179</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -4862,78 +4917,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8864AE-C8C6-47D9-9A9B-A8C6713BD64B}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5146,18 +5142,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF9BF5F-976E-4AED-80B0-D0C7BEF678BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF9BF5F-976E-4AED-80B0-D0C7BEF678BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6DC089-4E66-44B1-A5DD-17EE2077F65F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973A0928-5D64-4551-A2EF-5A5DE73A0408}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11340" yWindow="3672" windowWidth="17280" windowHeight="8964" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8E0284B2-DF31-49FE-BBC3-88D6CE9B6969}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpoint" sheetId="12" r:id="rId1"/>
@@ -38,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="219">
   <si>
     <t>/login</t>
-  </si>
-  <si>
-    <t>/student</t>
   </si>
   <si>
     <t>POST</t>
@@ -310,10 +306,6 @@
 zamítnutí přihlášky</t>
   </si>
   <si>
-    <t>JobApplicationStateRequest
-JobApplicationResponse</t>
-  </si>
-  <si>
     <t>JobApplicationDetailWithStudentResponse</t>
   </si>
   <si>
@@ -868,44 +860,56 @@
     <t>de/aktivace studenta</t>
   </si>
   <si>
+    <t>/job-offers</t>
+  </si>
+  <si>
+    <t>/job-offers/:id</t>
+  </si>
+  <si>
+    <t>/job-applications</t>
+  </si>
+  <si>
+    <t>/job-applications/:id</t>
+  </si>
+  <si>
+    <t>/groups</t>
+  </si>
+  <si>
+    <t>/groups/:id</t>
+  </si>
+  <si>
+    <t>student</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>operator</t>
+  </si>
+  <si>
+    <t>StudentRoleRequest</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>204
+404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">nesmí mít aktivní přihlášky
+nemá ban
 </t>
   </si>
   <si>
-    <t>/job-offers</t>
-  </si>
-  <si>
-    <t>/job-offers/:id</t>
-  </si>
-  <si>
-    <t>/job-applications</t>
-  </si>
-  <si>
-    <t>/job-applications/:id</t>
-  </si>
-  <si>
-    <t>/groups</t>
-  </si>
-  <si>
-    <t>/groups/:id</t>
-  </si>
-  <si>
-    <t>/customer</t>
-  </si>
-  <si>
-    <t>Redo</t>
-  </si>
-  <si>
-    <t>student</t>
-  </si>
-  <si>
-    <t>customer</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>operator</t>
+    <t>/students</t>
+  </si>
+  <si>
+    <t>/customers</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1117,7 +1121,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1140,6 +1143,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -2137,653 +2144,593 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="7"/>
-    <col min="2" max="2" width="34.44140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="3"/>
-    <col min="4" max="5" width="28.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="27.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="42.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="4" width="28.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33.109375" style="7" customWidth="1"/>
     <col min="9" max="9" width="50.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="33">
+        <v>201</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I6" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>178</v>
+      <c r="I14" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2</v>
+        <v>206</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>38</v>
+        <v>211</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>178</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>205</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>217</v>
+      <c r="E16" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>177</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="E18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>87</v>
+      <c r="A19" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>3</v>
+        <v>207</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="F21" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B20" s="28" t="s">
+      <c r="I21" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>205</v>
+      <c r="I22" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="A23" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B26:B30" xr:uid="{FDC17809-710E-4D0D-B138-FB947C15358B}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A26:A30" xr:uid="{FDC17809-710E-4D0D-B138-FB947C15358B}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -2805,140 +2752,140 @@
   <sheetData>
     <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
-        <v>178</v>
+      <c r="A2" s="30" t="s">
+        <v>176</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C3" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="B5" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="18" t="s">
+    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
+      <c r="C6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="6" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="7" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2949,7 +2896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A883F13D-779A-4F28-80DB-FE086864C46C}">
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.88671875" customWidth="1"/>
@@ -2960,648 +2907,663 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C6" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C7" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C11" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C12" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C13" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C14" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C16" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C17" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C18" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C19" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C21" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C22" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C24" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C25" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C28" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C29" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C31" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C32" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C33" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C34" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C36" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C38" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C40" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C42" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C43" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C44" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C45" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C46" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C48" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C49" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C50" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C51" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C52" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C53" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C54" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C55" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C56" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C57" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C59" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C60" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C61" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C62" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C63" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C64" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C65" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C67" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C69" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C70" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C71" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C73" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C74" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C75" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C76" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C77" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C78" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C80" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C81" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C83" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C85" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C87" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C88" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C89" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C91" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C92" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C93" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C95" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C96" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C97" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C98" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C99" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C101" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C102" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C103" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C104" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C105" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C106" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C107" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C108" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C109" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C110" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C111" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C112" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C113" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7"/>
       <c r="B114" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C115" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C116" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C118" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C119" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C120" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C122" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C123" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A2">
     <cfRule type="cellIs" dxfId="96" priority="82" operator="equal">
@@ -3938,7 +3900,7 @@
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A47 A41 A39 A27 A20 A58 A68 A79 A82 A90 A117 A86 A100" xr:uid="{8910B38B-79B6-4CCB-A1B0-31F905D2CB03}">
       <formula1>#REF!</formula1>
     </dataValidation>
@@ -3964,146 +3926,146 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="E1" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C4" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C6" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C8" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C10" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C11" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C14" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C16" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.3">
       <c r="D17" s="20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C18" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -4124,142 +4086,142 @@
   <sheetData>
     <row r="1" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>68</v>
-      </c>
       <c r="E1" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
-        <v>150</v>
+      <c r="A8" s="32" t="s">
+        <v>148</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>162</v>
-      </c>
       <c r="E10" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>161</v>
+        <v>151</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>159</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4278,6 +4240,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000918518D795C1C42B4BD6AFD3087D945" ma:contentTypeVersion="11" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="fc377329c2032e668f7168cd4dfdd1cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="029ce6df-f291-464d-b77d-f0e58d483ff7" xmlns:ns4="829f4f77-ad83-49f5-8a7e-f41738f3feaf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3d32f15185cfefe681f7660356c05bb" ns3:_="" ns4:_="">
     <xsd:import namespace="029ce6df-f291-464d-b77d-f0e58d483ff7"/>
@@ -4486,12 +4454,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF9BF5F-976E-4AED-80B0-D0C7BEF678BD}">
   <ds:schemaRefs>
@@ -4501,6 +4463,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B610B4-8AB9-48A0-8050-1CC6DB9C3AF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4517,13 +4488,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973A0928-5D64-4551-A2EF-5A5DE73A0408}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5E48DB-97EE-4A38-A884-51B6DB0A3FF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
-    <sheet name="endpoint" sheetId="12" r:id="rId1"/>
+    <sheet name="endpointy" sheetId="12" r:id="rId1"/>
     <sheet name="entity" sheetId="6" r:id="rId2"/>
     <sheet name="DTO" sheetId="9" r:id="rId3"/>
-    <sheet name="UI structure" sheetId="4" r:id="rId4"/>
-    <sheet name="bus. postupy" sheetId="10" r:id="rId5"/>
+    <sheet name="UI struktura" sheetId="4" r:id="rId4"/>
+    <sheet name="bus. logika" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="236">
   <si>
     <t>/login</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>Home</t>
-  </si>
-  <si>
-    <t>Funkce</t>
   </si>
   <si>
     <t>1. úroveň</t>
@@ -410,11 +407,6 @@
     <t>konkurence</t>
   </si>
   <si>
-    <t>musí být v budoucnosti
-není potvrzený zájemce
-pouze měnit status??</t>
-  </si>
-  <si>
     <t>AuthenticateResponse</t>
   </si>
   <si>
@@ -710,9 +702,6 @@
   </si>
   <si>
     <t>poznámky</t>
-  </si>
-  <si>
-    <t>marketing, úvod, …</t>
   </si>
   <si>
     <t>přihlášení, zapomenuté heslo</t>
@@ -910,6 +899,71 @@
   </si>
   <si>
     <t>/customers</t>
+  </si>
+  <si>
+    <t>musí být v budoucnosti
+není potvrzený zájemce
+pouze měnit</t>
+  </si>
+  <si>
+    <t>OperatorStudents</t>
+  </si>
+  <si>
+    <t>OperatorStudentDetail</t>
+  </si>
+  <si>
+    <t>aktivace, deaktivace</t>
+  </si>
+  <si>
+    <t>dodělávky</t>
+  </si>
+  <si>
+    <t>zavrhnuto</t>
+  </si>
+  <si>
+    <t>vývoj</t>
+  </si>
+  <si>
+    <t>přihlášení na nabídku</t>
+  </si>
+  <si>
+    <t>zrušení nabídky, detail</t>
+  </si>
+  <si>
+    <t>marketing, úvod</t>
+  </si>
+  <si>
+    <t>validace</t>
+  </si>
+  <si>
+    <t>validace
+design</t>
+  </si>
+  <si>
+    <t>filtr
+řazení</t>
+  </si>
+  <si>
+    <t>potvrzení zrušení</t>
+  </si>
+  <si>
+    <t>potvrzení změny</t>
+  </si>
+  <si>
+    <t>design
+validace</t>
+  </si>
+  <si>
+    <t>seznam studentů</t>
+  </si>
+  <si>
+    <t>Aktér</t>
+  </si>
+  <si>
+    <t>detaily</t>
+  </si>
+  <si>
+    <t>zrušeno</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1065,7 +1119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1117,10 +1171,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1142,11 +1194,23 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -2156,7 +2220,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>4</v>
@@ -2165,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>6</v>
@@ -2174,18 +2238,18 @@
         <v>12</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>175</v>
+      <c r="A2" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -2197,85 +2261,85 @@
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
-        <v>85</v>
+      <c r="A3" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="30">
         <v>201</v>
       </c>
-      <c r="H3" s="33">
-        <v>201</v>
-      </c>
       <c r="I3" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>176</v>
+      <c r="A4" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>175</v>
+      <c r="A5" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>13</v>
@@ -2284,448 +2348,448 @@
         <v>10</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>175</v>
+      <c r="A6" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>176</v>
+      <c r="A7" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>85</v>
+      <c r="A8" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
-        <v>176</v>
+      <c r="A9" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="I9" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="I10" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>84</v>
+      <c r="A11" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I11" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>175</v>
+      <c r="A12" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>85</v>
+      <c r="A13" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>85</v>
+      <c r="A14" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="E14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="I14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
-        <v>176</v>
+      <c r="A15" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
-        <v>176</v>
+      <c r="A16" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="I17" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
-        <v>175</v>
+      <c r="A18" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="26" t="s">
-        <v>85</v>
+      <c r="A19" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
-        <v>85</v>
+      <c r="A20" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>183</v>
+        <v>43</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
-        <v>174</v>
+      <c r="A21" s="25" t="s">
+        <v>172</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
-        <v>176</v>
+      <c r="A22" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
-        <v>84</v>
+      <c r="A23" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2752,7 +2816,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>14</v>
@@ -2765,127 +2829,127 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>176</v>
+      <c r="A2" s="28" t="s">
+        <v>174</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="C3" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="B5" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="6" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="7" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2907,7 +2971,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>14</v>
@@ -2922,645 +2986,645 @@
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C6" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C7" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C11" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C12" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C13" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C14" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C16" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C17" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C18" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C19" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C21" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C22" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C24" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C25" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C28" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C29" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C31" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C32" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C33" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C34" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C36" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C38" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C40" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C42" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C43" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C44" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C45" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C46" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C48" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C49" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C50" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C51" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C52" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C53" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C54" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C55" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C56" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C57" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C59" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C60" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C61" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C62" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C63" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C64" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C65" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C67" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C69" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C70" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C71" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C73" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C74" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C75" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C76" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C77" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C78" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C80" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C81" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C83" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C85" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C87" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C88" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C89" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C91" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C92" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C93" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C95" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C96" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C97" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C98" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C99" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C101" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C102" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C103" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C104" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C105" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C106" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C107" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C108" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C109" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C110" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C111" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C112" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C113" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7"/>
       <c r="B114" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C115" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C116" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C118" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C119" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C120" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B121" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C122" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C123" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
@@ -3915,157 +3979,327 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694BA3F6-B24A-4EB0-B375-4B8150629987}">
-  <dimension ref="B1:E18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="24" style="7" customWidth="1"/>
+    <col min="5" max="5" width="36.109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.5546875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="36"/>
+      <c r="E4" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="36"/>
+      <c r="E6" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="7" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F8" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="7" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C4" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F9" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="36"/>
+      <c r="E11" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="7" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C6" s="20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C8" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C11" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C14" s="20" t="s">
+      <c r="F14" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="E14" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="20" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="E15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C16" s="20" t="s">
+      <c r="D16" s="36"/>
+      <c r="E16" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D18" s="36"/>
+      <c r="E18" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="D17" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C18" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
+      <c r="F18" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -4076,152 +4310,407 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="22" t="s">
+    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="32" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="32" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="20" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="21" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="20" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="34" t="s">
         <v>171</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4240,12 +4729,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000918518D795C1C42B4BD6AFD3087D945" ma:contentTypeVersion="11" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="fc377329c2032e668f7168cd4dfdd1cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="029ce6df-f291-464d-b77d-f0e58d483ff7" xmlns:ns4="829f4f77-ad83-49f5-8a7e-f41738f3feaf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3d32f15185cfefe681f7660356c05bb" ns3:_="" ns4:_="">
     <xsd:import namespace="029ce6df-f291-464d-b77d-f0e58d483ff7"/>
@@ -4454,6 +4937,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF9BF5F-976E-4AED-80B0-D0C7BEF678BD}">
   <ds:schemaRefs>
@@ -4463,15 +4952,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B610B4-8AB9-48A0-8050-1CC6DB9C3AF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4488,4 +4968,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5E48DB-97EE-4A38-A884-51B6DB0A3FF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39483AD-D213-4FA1-8A7E-106ABCFA70B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpointy" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="235">
   <si>
     <t>/login</t>
   </si>
@@ -235,9 +235,6 @@
     </r>
   </si>
   <si>
-    <t>nabídka je v budoucnosti</t>
-  </si>
-  <si>
     <t>OperatorApplicationDetail</t>
   </si>
   <si>
@@ -944,12 +941,6 @@
 řazení</t>
   </si>
   <si>
-    <t>potvrzení zrušení</t>
-  </si>
-  <si>
-    <t>potvrzení změny</t>
-  </si>
-  <si>
     <t>design
 validace</t>
   </si>
@@ -964,6 +955,58 @@
   </si>
   <si>
     <t>zrušeno</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nabídka je v budoucnosti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nabídka patří k daté skupině</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+smazat i související přihlášky</t>
+    </r>
+  </si>
+  <si>
+    <t>204
+???</t>
   </si>
 </sst>
 </file>
@@ -2206,21 +2249,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9359BF-6886-4174-9CFB-71EFCF423033}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="4" width="28.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="50.5546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="3"/>
+    <col min="3" max="4" width="28.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="50.5703125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>4</v>
@@ -2229,7 +2272,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>6</v>
@@ -2241,15 +2284,15 @@
         <v>21</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -2267,79 +2310,79 @@
         <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H3" s="30">
         <v>201</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>13</v>
@@ -2348,90 +2391,90 @@
         <v>10</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>30</v>
@@ -2440,165 +2483,165 @@
         <v>31</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>83</v>
+    </row>
+    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>38</v>
+      <c r="F11" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="H11" s="6" t="s">
+        <v>234</v>
+      </c>
       <c r="I11" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="I14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>24</v>
@@ -2607,156 +2650,156 @@
         <v>36</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="I21" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>23</v>
@@ -2766,9 +2809,9 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>23</v>
@@ -2778,9 +2821,9 @@
       </c>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>23</v>
@@ -2806,17 +2849,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F046EC5E-0997-4F1F-89C0-BE0525D6DEB0}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
     <col min="3" max="3" width="47" style="7" customWidth="1"/>
     <col min="4" max="4" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>14</v>
@@ -2828,128 +2871,128 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="C3" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="C5" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="17" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C6" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="18" t="s">
+    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C7" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="7" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2961,17 +3004,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A883F13D-779A-4F28-80DB-FE086864C46C}">
   <dimension ref="A1:D124"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.88671875" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="49.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>14</v>
@@ -2983,651 +3026,651 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="D4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C6" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C12" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="7" t="s">
+    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C16" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C17" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="7" t="s">
+    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C21" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="7" t="s">
+    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="7" t="s">
+    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="7" t="s">
+    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="7" t="s">
+    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C28" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="7" t="s">
+    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="7" t="s">
+    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="7" t="s">
+    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="7" t="s">
+    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C38" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C40" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C42" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C43" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C46" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C48" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C49" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="7" t="s">
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="7" t="s">
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="7" t="s">
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="7" t="s">
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7"/>
       <c r="B68" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C70" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C73" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="7" t="s">
+    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="7" t="s">
+    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="7" t="s">
+    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C80" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C81" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C83" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C85" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C87" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C88" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C89" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C91" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C92" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C95" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C96" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C97" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C99" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C101" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C102" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="7" t="s">
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C104" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C105" s="7" t="s">
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="7" t="s">
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C107" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="7" t="s">
+    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C111" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="7" t="s">
+    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7"/>
       <c r="B114" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C115" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C116" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C118" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C119" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C120" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C122" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C123" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="A2">
     <cfRule type="cellIs" dxfId="96" priority="82" operator="equal">
@@ -3980,19 +4023,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694BA3F6-B24A-4EB0-B375-4B8150629987}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.21875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" style="7" customWidth="1"/>
     <col min="4" max="4" width="24" style="7" customWidth="1"/>
-    <col min="5" max="5" width="36.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="27.5546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>18</v>
@@ -4010,9 +4053,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="36" t="s">
         <v>17</v>
@@ -4020,12 +4063,12 @@
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
       <c r="E2" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>16</v>
@@ -4033,273 +4076,261 @@
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
       <c r="E3" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
       <c r="E5" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="36"/>
       <c r="C6" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D6" s="36"/>
       <c r="E6" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
       <c r="E7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="36"/>
       <c r="D9" s="36"/>
       <c r="E9" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B10" s="36"/>
       <c r="C10" s="36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
-        <v>222</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
       <c r="D12" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="36" t="s">
         <v>138</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>139</v>
       </c>
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
       <c r="E13" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="36"/>
       <c r="E14" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
       <c r="E15" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="36"/>
       <c r="C16" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="F17" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" s="36"/>
       <c r="C18" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="36"/>
       <c r="E18" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C19" s="36"/>
       <c r="D19" s="36"/>
       <c r="E19" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D20" s="36"/>
       <c r="E20" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4311,406 +4342,407 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="B2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="33" t="s">
+      <c r="B26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="33" t="s">
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="34" t="s">
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="34" t="s">
         <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39483AD-D213-4FA1-8A7E-106ABCFA70B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69673B90-4FE4-453E-9F1E-F0A3D9FDABF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpointy" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="239">
   <si>
     <t>/login</t>
   </si>
@@ -1007,6 +1007,19 @@
   <si>
     <t>204
 ???</t>
+  </si>
+  <si>
+    <t>/students/:id</t>
+  </si>
+  <si>
+    <t>detail studenta</t>
+  </si>
+  <si>
+    <t>200
+404</t>
+  </si>
+  <si>
+    <t>i jeho hodnocení</t>
   </si>
 </sst>
 </file>
@@ -2248,20 +2261,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9359BF-6886-4174-9CFB-71EFCF423033}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="3"/>
-    <col min="3" max="4" width="28.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="50.5703125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="4" width="28.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33.109375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="50.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>81</v>
       </c>
@@ -2290,7 +2303,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>172</v>
       </c>
@@ -2316,7 +2329,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>83</v>
       </c>
@@ -2342,7 +2355,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>173</v>
       </c>
@@ -2368,7 +2381,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>172</v>
       </c>
@@ -2376,25 +2389,26 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H5" s="7">
+        <v>200</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>172</v>
       </c>
@@ -2402,96 +2416,103 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>78</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>173</v>
+        <v>238</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>172</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>205</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>173</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>220</v>
+        <v>79</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>200</v>
@@ -2500,165 +2521,165 @@
         <v>206</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>173</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>206</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
         <v>172</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>205</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>48</v>
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
-        <v>173</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>207</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>183</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
-        <v>173</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>205</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>173</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>202</v>
@@ -2667,93 +2688,96 @@
         <v>207</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>210</v>
+        <v>47</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
-        <v>172</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>205</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>83</v>
+        <v>24</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>207</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>203</v>
@@ -2762,66 +2786,85 @@
         <v>207</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
-        <v>173</v>
+        <v>71</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>207</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
         <v>82</v>
       </c>
@@ -2829,15 +2872,39 @@
         <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A26:A30" xr:uid="{FDC17809-710E-4D0D-B138-FB947C15358B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A28:A32" xr:uid="{FDC17809-710E-4D0D-B138-FB947C15358B}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -2849,15 +2916,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F046EC5E-0997-4F1F-89C0-BE0525D6DEB0}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="47" style="7" customWidth="1"/>
     <col min="4" max="4" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>81</v>
       </c>
@@ -2871,7 +2938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>173</v>
       </c>
@@ -2885,7 +2952,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>187</v>
       </c>
@@ -2899,7 +2966,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
         <v>173</v>
       </c>
@@ -2913,7 +2980,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>189</v>
       </c>
@@ -2927,7 +2994,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
         <v>173</v>
       </c>
@@ -2941,7 +3008,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
         <v>173</v>
       </c>
@@ -2955,7 +3022,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>82</v>
       </c>
@@ -2963,7 +3030,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>82</v>
       </c>
@@ -2971,7 +3038,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>82</v>
       </c>
@@ -2979,7 +3046,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>82</v>
       </c>
@@ -2987,7 +3054,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>82</v>
       </c>
@@ -3004,15 +3071,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A883F13D-779A-4F28-80DB-FE086864C46C}">
   <dimension ref="A1:D124"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="33.88671875" customWidth="1"/>
+    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="49.88671875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>81</v>
       </c>
@@ -3026,13 +3093,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
         <v>103</v>
       </c>
@@ -3040,7 +3107,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
         <v>104</v>
       </c>
@@ -3048,34 +3115,34 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C6" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C7" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7" t="s">
         <v>103</v>
       </c>
@@ -3083,7 +3150,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C11" s="7" t="s">
         <v>104</v>
       </c>
@@ -3091,586 +3158,586 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C12" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C13" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C14" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C16" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C17" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C18" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C19" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C21" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C22" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C24" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C25" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C28" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C29" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C30" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C31" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C32" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C33" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C34" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C35" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C36" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C38" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C40" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C42" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C43" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C44" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C45" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C46" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C48" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C49" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C50" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C51" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C52" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C53" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C54" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C55" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C56" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C57" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C59" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C60" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C61" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C62" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C63" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C64" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C65" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C67" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C69" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C70" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C71" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C73" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C74" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C75" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C76" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C77" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C78" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C80" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C81" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C83" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C85" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C87" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C88" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C89" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C91" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C92" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C93" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C95" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C96" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C97" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C98" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C99" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C101" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C102" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C103" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C104" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C105" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C106" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C107" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C108" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C109" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C110" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C111" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C112" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C113" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7"/>
       <c r="B114" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C115" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C116" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C118" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C119" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C120" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B121" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C122" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C123" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="A2">
     <cfRule type="cellIs" dxfId="96" priority="82" operator="equal">
@@ -4023,17 +4090,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694BA3F6-B24A-4EB0-B375-4B8150629987}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="7" customWidth="1"/>
     <col min="4" max="4" width="24" style="7" customWidth="1"/>
-    <col min="5" max="5" width="36.140625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="36.109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.5546875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>81</v>
       </c>
@@ -4053,7 +4120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>82</v>
       </c>
@@ -4066,7 +4133,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>219</v>
       </c>
@@ -4082,7 +4149,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
         <v>221</v>
       </c>
@@ -4098,7 +4165,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
         <v>221</v>
       </c>
@@ -4114,7 +4181,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>83</v>
       </c>
@@ -4127,7 +4194,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
         <v>221</v>
       </c>
@@ -4143,7 +4210,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>83</v>
       </c>
@@ -4156,7 +4223,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
         <v>221</v>
       </c>
@@ -4172,7 +4239,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
         <v>221</v>
       </c>
@@ -4188,7 +4255,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>83</v>
       </c>
@@ -4201,7 +4268,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
         <v>220</v>
       </c>
@@ -4214,7 +4281,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
         <v>221</v>
       </c>
@@ -4230,7 +4297,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
         <v>83</v>
       </c>
@@ -4243,7 +4310,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
         <v>221</v>
       </c>
@@ -4259,7 +4326,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
         <v>83</v>
       </c>
@@ -4272,7 +4339,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
         <v>221</v>
       </c>
@@ -4288,7 +4355,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>221</v>
       </c>
@@ -4304,7 +4371,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>82</v>
       </c>
@@ -4320,7 +4387,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>82</v>
       </c>
@@ -4342,14 +4409,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>81</v>
       </c>
@@ -4360,7 +4427,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>221</v>
       </c>
@@ -4371,7 +4438,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>231</v>
       </c>
@@ -4382,7 +4449,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>82</v>
       </c>
@@ -4393,7 +4460,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>82</v>
       </c>
@@ -4404,7 +4471,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
         <v>221</v>
       </c>
@@ -4415,7 +4482,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
         <v>221</v>
       </c>
@@ -4426,7 +4493,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
         <v>221</v>
       </c>
@@ -4437,7 +4504,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>231</v>
       </c>
@@ -4448,7 +4515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
         <v>82</v>
       </c>
@@ -4459,7 +4526,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>82</v>
       </c>
@@ -4470,7 +4537,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="33" t="s">
         <v>82</v>
       </c>
@@ -4481,7 +4548,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="33" t="s">
         <v>82</v>
       </c>
@@ -4492,7 +4559,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>231</v>
       </c>
@@ -4503,7 +4570,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
         <v>221</v>
       </c>
@@ -4514,7 +4581,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>231</v>
       </c>
@@ -4525,7 +4592,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>231</v>
       </c>
@@ -4536,7 +4603,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>231</v>
       </c>
@@ -4547,7 +4614,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>231</v>
       </c>
@@ -4558,7 +4625,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>83</v>
       </c>
@@ -4569,7 +4636,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="33" t="s">
         <v>82</v>
       </c>
@@ -4580,7 +4647,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>83</v>
       </c>
@@ -4591,7 +4658,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>82</v>
       </c>
@@ -4602,7 +4669,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="33" t="s">
         <v>82</v>
       </c>
@@ -4613,7 +4680,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="33" t="s">
         <v>82</v>
       </c>
@@ -4624,7 +4691,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>83</v>
       </c>
@@ -4635,7 +4702,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
         <v>83</v>
       </c>
@@ -4646,7 +4713,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
         <v>231</v>
       </c>
@@ -4657,7 +4724,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
         <v>231</v>
       </c>
@@ -4668,7 +4735,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="32" t="s">
         <v>232</v>
       </c>
@@ -4679,7 +4746,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="20" t="s">
         <v>231</v>
       </c>
@@ -4690,7 +4757,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
         <v>231</v>
       </c>
@@ -4701,7 +4768,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
         <v>83</v>
       </c>
@@ -4712,7 +4779,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>82</v>
       </c>
@@ -4723,7 +4790,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>83</v>
       </c>
@@ -4734,7 +4801,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>82</v>
       </c>

--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69673B90-4FE4-453E-9F1E-F0A3D9FDABF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9205B9FE-C09A-424F-9763-76B63CB39335}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpointy" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="231">
   <si>
     <t>/login</t>
   </si>
@@ -137,12 +137,6 @@
     <t>musí být do budoucnousti
 start je před koncem
 doba min. 1h</t>
-  </si>
-  <si>
-    <t>úprava pracovní nabídky</t>
-  </si>
-  <si>
-    <t>schválení úprav zájemcem</t>
   </si>
   <si>
     <t>smazání pracovní nabídky</t>
@@ -321,12 +315,6 @@
     <t>Student</t>
   </si>
   <si>
-    <t>StudentId
-FirstName
-LastName
-DateOfBirth</t>
-  </si>
-  <si>
     <t>Customer</t>
   </si>
   <si>
@@ -340,16 +328,6 @@
   </si>
   <si>
     <t>JobOffer</t>
-  </si>
-  <si>
-    <t>JobOfferId
-Title
-Description
-Wage
-Spaces
-Start
-End
-GroupId</t>
   </si>
   <si>
     <t>JobApplication</t>
@@ -563,9 +541,6 @@
     <t>CustomerSimleResponse</t>
   </si>
   <si>
-    <t>datum podání</t>
-  </si>
-  <si>
     <t>StudentJobOffers</t>
   </si>
   <si>
@@ -590,9 +565,6 @@
     <t>CustomerJobOfferDetail</t>
   </si>
   <si>
-    <t>CustomerJobOfferEdit</t>
-  </si>
-  <si>
     <t>OperatorJobApplications</t>
   </si>
   <si>
@@ -638,9 +610,6 @@
     <t>vytvoření nabídky</t>
   </si>
   <si>
-    <t>úprava nabídky</t>
-  </si>
-  <si>
     <t>prohlížení nabídek skupiny</t>
   </si>
   <si>
@@ -681,12 +650,6 @@
   </si>
   <si>
     <t>zrušení skupiny</t>
-  </si>
-  <si>
-    <t>úprava účtu (ověření?)</t>
-  </si>
-  <si>
-    <t>nastavení balíčku</t>
   </si>
   <si>
     <t>úprava účtu (ověření)</t>
@@ -805,35 +768,12 @@
 promyslet aktivaci</t>
   </si>
   <si>
-    <t>adresa
-další info</t>
-  </si>
-  <si>
     <t>poznámky
 promyslet hodnocení
 promyslet bus plan</t>
   </si>
   <si>
-    <t>adresa
-další info
-datum vytvoření</t>
-  </si>
-  <si>
-    <t>adresa
-datum vytvoření
-kategorie?</t>
-  </si>
-  <si>
-    <t>Adresa?</t>
-  </si>
-  <si>
     <t>Baliček?</t>
-  </si>
-  <si>
-    <t>Hodnoceni?</t>
-  </si>
-  <si>
-    <t>PracovniPotvrzeni?</t>
   </si>
   <si>
     <t>Vyplatnice?</t>
@@ -898,11 +838,6 @@
     <t>/customers</t>
   </si>
   <si>
-    <t>musí být v budoucnosti
-není potvrzený zájemce
-pouze měnit</t>
-  </si>
-  <si>
     <t>OperatorStudents</t>
   </si>
   <si>
@@ -913,9 +848,6 @@
   </si>
   <si>
     <t>dodělávky</t>
-  </si>
-  <si>
-    <t>zavrhnuto</t>
   </si>
   <si>
     <t>vývoj</t>
@@ -952,9 +884,6 @@
   </si>
   <si>
     <t>detaily</t>
-  </si>
-  <si>
-    <t>zrušeno</t>
   </si>
   <si>
     <r>
@@ -1020,6 +949,76 @@
   </si>
   <si>
     <t>i jeho hodnocení</t>
+  </si>
+  <si>
+    <t>GroupWithIdRequest</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>název</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+balíček</t>
+    </r>
+  </si>
+  <si>
+    <t>úprava účtu</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>AddressId
+Country
+City
+Street
+Number</t>
+  </si>
+  <si>
+    <t>StudentId
+FirstName
+LastName
+DateOfBirth
+AddressId</t>
+  </si>
+  <si>
+    <t>další info
+datum vytvoření</t>
+  </si>
+  <si>
+    <t>datum vytvoření
+kategorie?</t>
+  </si>
+  <si>
+    <t>JobOfferId
+Title
+Description
+Wage
+Spaces
+Start
+End
+GroupId
+AddressId</t>
+  </si>
+  <si>
+    <t>datum podání
+počet hodin</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1100,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1156,12 +1155,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1175,7 +1168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1253,17 +1246,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2262,21 +2248,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9359BF-6886-4174-9CFB-71EFCF423033}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="4" width="28.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="50.5546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="3"/>
+    <col min="3" max="4" width="28.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="50.5703125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>4</v>
@@ -2285,7 +2271,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>6</v>
@@ -2297,15 +2283,15 @@
         <v>21</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -2323,79 +2309,79 @@
         <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="H3" s="30">
         <v>201</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
@@ -2405,51 +2391,51 @@
         <v>200</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
@@ -2458,90 +2444,90 @@
         <v>10</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
         <v>79</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>30</v>
@@ -2550,21 +2536,21 @@
         <v>31</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>220</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>32</v>
@@ -2575,298 +2561,298 @@
       <c r="G12" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
-        <v>173</v>
+      <c r="H12" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>163</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>233</v>
+        <v>42</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>234</v>
+        <v>10</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
-        <v>83</v>
+        <v>45</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
+        <v>40</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>170</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>83</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>23</v>
@@ -2876,9 +2862,9 @@
       </c>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
@@ -2888,9 +2874,9 @@
       </c>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>23</v>
@@ -2915,18 +2901,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F046EC5E-0997-4F1F-89C0-BE0525D6DEB0}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
     <col min="3" max="3" width="47" style="7" customWidth="1"/>
     <col min="4" max="4" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>14</v>
@@ -2938,128 +2924,115 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C3" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D4" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="C5" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C6" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>82</v>
+      <c r="D7" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>164</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3071,17 +3044,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A883F13D-779A-4F28-80DB-FE086864C46C}">
   <dimension ref="A1:D124"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.88671875" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="49.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>14</v>
@@ -3093,651 +3066,651 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C6" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="7" t="s">
+    </row>
+    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C14" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C16" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C18" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C19" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C21" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="7" t="s">
+    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C28" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="7" t="s">
+    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
+    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C38" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C40" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C42" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C43" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="7" t="s">
+    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C48" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C49" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="7" t="s">
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="7" t="s">
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C59" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="7" t="s">
+    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C67" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7"/>
       <c r="B68" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C69" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C70" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C71" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C73" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C80" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C81" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7"/>
       <c r="B82" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C83" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C85" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C87" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C88" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C89" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C91" s="7" t="s">
+    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C92" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C93" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C95" s="7" t="s">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C96" s="7" t="s">
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C99" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C101" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C102" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C104" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C105" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C107" s="7" t="s">
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="7" t="s">
+    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C111" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C112" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C113" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7"/>
       <c r="B114" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C115" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C116" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C118" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C119" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C120" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C122" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C123" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" collapsed="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="A2">
     <cfRule type="cellIs" dxfId="96" priority="82" operator="equal">
@@ -4089,20 +4062,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694BA3F6-B24A-4EB0-B375-4B8150629987}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" style="7" customWidth="1"/>
     <col min="4" max="4" width="24" style="7" customWidth="1"/>
-    <col min="5" max="5" width="36.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="27.5546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>18</v>
@@ -4120,284 +4093,271 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
       <c r="E2" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="7" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36" t="s">
+      <c r="D10" s="34"/>
+      <c r="E10" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="D11" s="34"/>
+      <c r="E11" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36" t="s">
-        <v>137</v>
-      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+        <v>42</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="34"/>
       <c r="E13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B15" s="36" t="s">
+      <c r="D15" s="34"/>
+      <c r="E15" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36" t="s">
-        <v>75</v>
-      </c>
+      <c r="D17" s="34"/>
       <c r="E17" s="7" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="36"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="7" t="s">
-        <v>43</v>
+        <v>212</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
+        <v>78</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="34"/>
       <c r="E19" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="7" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4408,408 +4368,375 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
-  <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="C1" s="21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C2" s="34" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="34" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="34" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="32" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4828,6 +4755,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000918518D795C1C42B4BD6AFD3087D945" ma:contentTypeVersion="11" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="fc377329c2032e668f7168cd4dfdd1cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="029ce6df-f291-464d-b77d-f0e58d483ff7" xmlns:ns4="829f4f77-ad83-49f5-8a7e-f41738f3feaf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3d32f15185cfefe681f7660356c05bb" ns3:_="" ns4:_="">
     <xsd:import namespace="029ce6df-f291-464d-b77d-f0e58d483ff7"/>
@@ -5036,12 +4969,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF9BF5F-976E-4AED-80B0-D0C7BEF678BD}">
   <ds:schemaRefs>
@@ -5051,6 +4978,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B610B4-8AB9-48A0-8050-1CC6DB9C3AF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5067,13 +5003,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/analýza.xlsx
+++ b/analýza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programování\Studentby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9205B9FE-C09A-424F-9763-76B63CB39335}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5120DE7A-89E6-4256-B077-A03E2F990AD8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{DB6EC42D-789E-43C7-919C-4D2FCCC7560E}"/>
   </bookViews>
   <sheets>
     <sheet name="endpointy" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="232">
   <si>
     <t>/login</t>
   </si>
@@ -1019,6 +1019,9 @@
   <si>
     <t>datum podání
 počet hodin</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -4368,7 +4371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92F6529-D796-4CD7-9C82-041582C2B24B}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -4376,7 +4379,7 @@
     <col min="3" max="3" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
@@ -4387,7 +4390,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>204</v>
       </c>
@@ -4397,8 +4400,11 @@
       <c r="C2" s="32" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>214</v>
       </c>
@@ -4408,8 +4414,11 @@
       <c r="C3" s="32" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>78</v>
       </c>
@@ -4419,8 +4428,11 @@
       <c r="C4" s="32" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>78</v>
       </c>
@@ -4430,8 +4442,11 @@
       <c r="C5" s="32" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>204</v>
       </c>
@@ -4441,8 +4456,11 @@
       <c r="C6" s="32" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>204</v>
       </c>
@@ -4452,8 +4470,11 @@
       <c r="C7" s="32" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>204</v>
       </c>
@@ -4463,8 +4484,11 @@
       <c r="C8" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>214</v>
       </c>
@@ -4474,8 +4498,11 @@
       <c r="C9" s="32" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>204</v>
       </c>
@@ -4485,8 +4512,11 @@
       <c r="C10" s="32" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>78</v>
       </c>
@@ -4496,8 +4526,11 @@
       <c r="C11" s="32" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
         <v>78</v>
       </c>
@@ -4507,8 +4540,11 @@
       <c r="C12" s="32" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>214</v>
       </c>
@@ -4518,8 +4554,11 @@
       <c r="C13" s="32" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>204</v>
       </c>
@@ -4529,8 +4568,11 @@
       <c r="C14" s="35" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>214</v>
       </c>
@@ -4540,8 +4582,11 @@
       <c r="C15" s="32" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>214</v>
       </c>
@@ -4551,8 +4596,11 @@
       <c r="C16" s="32" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>214</v>
       </c>
@@ -4562,8 +4610,11 @@
       <c r="C17" s="32" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>214</v>
       </c>
@@ -4573,8 +4624,11 @@
       <c r="C18" s="32" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>79</v>
       </c>
@@ -4584,8 +4638,11 @@
       <c r="C19" s="32" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>78</v>
       </c>
@@ -4595,8 +4652,11 @@
       <c r="C20" s="32" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>79</v>
       </c>
@@ -4606,8 +4666,11 @@
       <c r="C21" s="32" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>78</v>
       </c>
@@ -4617,8 +4680,11 @@
       <c r="C22" s="32" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
         <v>78</v>
       </c>
@@ -4628,8 +4694,11 @@
       <c r="C23" s="32" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>79</v>
       </c>
@@ -4639,8 +4708,11 @@
       <c r="C24" s="32" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>79</v>
       </c>
@@ -4650,8 +4722,11 @@
       <c r="C25" s="32" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>214</v>
       </c>
@@ -4661,8 +4736,11 @@
       <c r="C26" s="32" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>214</v>
       </c>
@@ -4673,7 +4751,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>214</v>
       </c>
@@ -4684,7 +4762,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>214</v>
       </c>
@@ -4695,7 +4773,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>79</v>
       </c>
@@ -4706,7 +4784,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
         <v>78</v>
       </c>
@@ -4717,7 +4795,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>79</v>
       </c>
@@ -4755,12 +4833,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000918518D795C1C42B4BD6AFD3087D945" ma:contentTypeVersion="11" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="fc377329c2032e668f7168cd4dfdd1cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="029ce6df-f291-464d-b77d-f0e58d483ff7" xmlns:ns4="829f4f77-ad83-49f5-8a7e-f41738f3feaf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3d32f15185cfefe681f7660356c05bb" ns3:_="" ns4:_="">
     <xsd:import namespace="029ce6df-f291-464d-b77d-f0e58d483ff7"/>
@@ -4969,6 +5041,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF9BF5F-976E-4AED-80B0-D0C7BEF678BD}">
   <ds:schemaRefs>
@@ -4978,15 +5056,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B610B4-8AB9-48A0-8050-1CC6DB9C3AF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5003,4 +5072,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531A14DD-C053-44BA-9FCD-D617CDE7C93D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>